--- a/backtest_runs/20260410_193731/filter/BAPL/BAPL.xlsx
+++ b/backtest_runs/20260410_193731/filter/BAPL/BAPL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-2817.649999999991</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>97182.35000000001</v>
@@ -633,7 +633,7 @@
         <v>-4368.649999999994</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>92968.8</v>
@@ -679,7 +679,7 @@
         <v>-1163.250000000007</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>91805.54999999999</v>
@@ -817,7 +817,7 @@
         <v>-25.84999999999486</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>100723.8</v>
@@ -863,7 +863,7 @@
         <v>-7574.049999999999</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>93149.75</v>
@@ -909,7 +909,7 @@
         <v>-930.5999999999985</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>92219.15000000001</v>
@@ -955,7 +955,7 @@
         <v>-2016.300000000003</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>90202.85000000001</v>
@@ -1185,7 +1185,7 @@
         <v>-1809.500000000007</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>108220.3</v>
@@ -1323,7 +1323,7 @@
         <v>-1085.700000000004</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>110986.25</v>
@@ -1415,7 +1415,7 @@
         <v>-51.70000000000808</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>114941.3</v>
@@ -1507,7 +1507,7 @@
         <v>-2559.150000000005</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>115044.7</v>
@@ -1599,7 +1599,7 @@
         <v>-491.1500000000125</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>116724.95</v>
@@ -1645,7 +1645,7 @@
         <v>-2921.049999999988</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>113803.9</v>
